--- a/AAII_Financials/Yearly/PAX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PAX_YR_FIN.xlsx
@@ -1950,10 +1950,10 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>35100</v>
+        <v>168400</v>
       </c>
       <c r="E42" s="3">
-        <v>5000</v>
+        <v>22600</v>
       </c>
       <c r="F42" s="3">
         <v>17200</v>
@@ -2076,10 +2076,10 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>174000</v>
+        <v>40700</v>
       </c>
       <c r="E45" s="3">
-        <v>100100</v>
+        <v>82400</v>
       </c>
       <c r="F45" s="3">
         <v>227700</v>
@@ -2160,10 +2160,10 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>44600</v>
+        <v>90800</v>
       </c>
       <c r="E47" s="3">
-        <v>50000</v>
+        <v>57600</v>
       </c>
       <c r="F47" s="3">
         <v>58600</v>
@@ -2370,10 +2370,10 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>56000</v>
+        <v>9800</v>
       </c>
       <c r="E52" s="3">
-        <v>14100</v>
+        <v>6600</v>
       </c>
       <c r="F52" s="3">
         <v>4500</v>
@@ -2700,7 +2700,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>194400</v>
+        <v>262700</v>
       </c>
       <c r="E61" s="3">
         <v>168200</v>
@@ -2742,7 +2742,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>200000</v>
+        <v>131600</v>
       </c>
       <c r="E62" s="3">
         <v>147800</v>
